--- a/boring_stuff/dimensions.xlsx
+++ b/boring_stuff/dimensions.xlsx
@@ -1,28 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<s:workbook xmlns:s="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <s:fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <s:workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <s:bookViews>
-    <s:workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
-  </s:bookViews>
-  <s:sheets>
-    <s:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" r:id="rId1"/>
-  </s:sheets>
-  <s:definedNames/>
-  <s:calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1"/>
-</s:workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2">
-  <si>
-    <t>Tall row</t>
-  </si>
-  <si>
-    <t>Wide column</t>
-  </si>
-</sst>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30,16 +19,16 @@
   <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -55,16 +44,83 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -352,27 +408,32 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" customHeight="1" ht="70.0">
-      <c r="A1" t="s">
-        <v>0</v>
+    <row r="1" ht="70" customHeight="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Tall row</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="B2" t="s">
-        <v>1</v>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Wide column</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins right="0.75" top="1" bottom="1" left="0.75" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>